--- a/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_SFH_until_2004_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_SFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>16.52857859597958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>134520.7735261632</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>15.93920584694646</v>
       </c>
       <c r="G2" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>51.79481913822178</v>
       </c>
       <c r="I2" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>41.02372475085344</v>
       </c>
       <c r="K2" t="n">
         <v>134520.7735261632</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>75.97972107562408</v>
+        <v>104.7820615717713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>134520.7735261632</v>
       </c>
       <c r="F3" t="n">
-        <v>98.06892977262093</v>
+        <v>104.1813221980475</v>
       </c>
       <c r="G3" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="H3" t="n">
-        <v>421.3660232015465</v>
+        <v>122.7667304532371</v>
       </c>
       <c r="I3" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="J3" t="n">
-        <v>281.5955583479916</v>
+        <v>121.5524237633324</v>
       </c>
       <c r="K3" t="n">
         <v>134520.7735261632</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>569.3184702522215</v>
+        <v>255.0219289514113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>134520.7735261632</v>
       </c>
       <c r="F4" t="n">
-        <v>581.6297002353539</v>
+        <v>344.7939229672424</v>
       </c>
       <c r="G4" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="H4" t="n">
-        <v>507.8213586794238</v>
+        <v>299.6853922506806</v>
       </c>
       <c r="I4" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="J4" t="n">
-        <v>574.637101608873</v>
+        <v>297.0805126105475</v>
       </c>
       <c r="K4" t="n">
         <v>134520.7735261632</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>734.4317171200331</v>
+        <v>392.4293248751547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>134520.7735261632</v>
       </c>
       <c r="F5" t="n">
-        <v>743.4710655534518</v>
+        <v>363.9219159499522</v>
       </c>
       <c r="G5" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="H5" t="n">
-        <v>507.8213586794238</v>
+        <v>389.9533085144799</v>
       </c>
       <c r="I5" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="J5" t="n">
-        <v>665.601753187977</v>
+        <v>389.9533085144799</v>
       </c>
       <c r="K5" t="n">
         <v>134520.7735261632</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>734.4317171200331</v>
+        <v>459.704548615538</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>134520.7735261632</v>
       </c>
       <c r="F6" t="n">
-        <v>743.4710655534517</v>
+        <v>459.7045486155386</v>
       </c>
       <c r="G6" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="H6" t="n">
-        <v>507.8213586794238</v>
+        <v>563.3408620321728</v>
       </c>
       <c r="I6" t="n">
         <v>134520.7735261632</v>
       </c>
       <c r="J6" t="n">
-        <v>665.601753187977</v>
+        <v>577.712701911703</v>
       </c>
       <c r="K6" t="n">
         <v>134520.7735261632</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>107.6457013111799</v>
+        <v>92.98255377694794</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>107.6457013111799</v>
+        <v>92.98255377694794</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>141.5576224207508</v>
+        <v>122.2751032224203</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>141.5576224207508</v>
+        <v>122.2751032224203</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>157.2842635249378</v>
+        <v>135.8595123942611</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>157.2842635249378</v>
+        <v>135.8595123942611</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>166.1575103036609</v>
+        <v>143.5240743389476</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>166.1575103036609</v>
+        <v>143.5240743389476</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>201.7811602892447</v>
+        <v>174.2951865168539</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>171.8118565715436</v>
+        <v>148.4082039374631</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>171.8118565715436</v>
+        <v>148.4082039374631</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02698353127058824</v>
+        <v>0.02346394023529412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02698353127058824</v>
+        <v>0.0232188253882353</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02698353127058824</v>
+        <v>0.02463713724705883</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02698353127058824</v>
+        <v>0.02463713724705883</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02698353127058824</v>
+        <v>0.02463713724705883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02463713724705883</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02564844589152239</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02575583355424959</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02581033425882353</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02627439438279591</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02627437534117648</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02815672828235295</v>
+        <v>0.02627437534117648</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02698412698412699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02698412698412699</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02797903591958902</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02808649703127611</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02698412698412699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02698412698412699</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02797903591958902</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03167631931764706</v>
+        <v>0.02808649703127611</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2.472098519390803</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>20.94156666</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.246511709139669</v>
       </c>
       <c r="G19" t="n">
         <v>20.94156666</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.869782737499997</v>
       </c>
       <c r="I19" t="n">
         <v>20.94156666</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.869782737499997</v>
       </c>
       <c r="K19" t="n">
         <v>20.94156666</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2.493043649999998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>20.94156666</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.493043650000002</v>
       </c>
       <c r="G20" t="n">
         <v>20.94156666</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.964181805218333</v>
       </c>
       <c r="I20" t="n">
         <v>20.94156666</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.907093089634567</v>
       </c>
       <c r="K20" t="n">
         <v>20.94156666</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2.493043649999998</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>20.94156666</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.493043649999998</v>
       </c>
       <c r="G21" t="n">
         <v>20.94156666</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.964181805218333</v>
       </c>
       <c r="I21" t="n">
         <v>20.94156666</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.907093089634567</v>
       </c>
       <c r="K21" t="n">
         <v>20.94156666</v>
@@ -2364,13 +2364,13 @@
         <v>162.5786571839789</v>
       </c>
       <c r="H52" t="n">
-        <v>1.389202363027753</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>46.87382139989371</v>
       </c>
       <c r="J52" t="n">
-        <v>1.537136825225346</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>46.87382139989371</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>15.40370809076779</v>
+        <v>14.48431634788585</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F53" t="n">
-        <v>14.62314688127522</v>
+        <v>12.26434106274649</v>
       </c>
       <c r="G53" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H53" t="n">
-        <v>23.1225457900752</v>
+        <v>15.56196467578361</v>
       </c>
       <c r="I53" t="n">
         <v>67.78822935338276</v>
       </c>
       <c r="J53" t="n">
-        <v>28.61842318038532</v>
+        <v>13.96849176946057</v>
       </c>
       <c r="K53" t="n">
         <v>67.78822935338276</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>40.36320322129337</v>
+        <v>40.59309269134269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F54" t="n">
-        <v>39.51667268164874</v>
+        <v>37.31817469310977</v>
       </c>
       <c r="G54" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H54" t="n">
-        <v>43.31764655124653</v>
+        <v>44.89476474013829</v>
       </c>
       <c r="I54" t="n">
         <v>79.15968192647779</v>
       </c>
       <c r="J54" t="n">
-        <v>48.12554143274598</v>
+        <v>43.359731094705</v>
       </c>
       <c r="K54" t="n">
         <v>79.15968192647779</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>41.81995579476277</v>
+        <v>41.35643678052298</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F55" t="n">
-        <v>40.22123032175868</v>
+        <v>38.951024334506</v>
       </c>
       <c r="G55" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H55" t="n">
-        <v>46.37175012416222</v>
+        <v>54.33645331097275</v>
       </c>
       <c r="I55" t="n">
         <v>86.15967967961915</v>
       </c>
       <c r="J55" t="n">
-        <v>53.36378336604977</v>
+        <v>48.22590188302919</v>
       </c>
       <c r="K55" t="n">
         <v>86.15967967961915</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>41.81995579476277</v>
+        <v>40.72442778224063</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F56" t="n">
-        <v>38.51653002660377</v>
+        <v>39.6763213903211</v>
       </c>
       <c r="G56" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H56" t="n">
-        <v>44.2511791743146</v>
+        <v>53.27526648864494</v>
       </c>
       <c r="I56" t="n">
         <v>90.86041773576243</v>
       </c>
       <c r="J56" t="n">
-        <v>52.19058635428507</v>
+        <v>49.7718871697477</v>
       </c>
       <c r="K56" t="n">
         <v>90.86041773576243</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>13.86473320822596</v>
+        <v>2.708290051364088</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F64" t="n">
-        <v>14.43969249824267</v>
+        <v>3.5</v>
       </c>
       <c r="G64" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H64" t="n">
-        <v>24.94181060235305</v>
+        <v>5.418438461991201</v>
       </c>
       <c r="I64" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="J64" t="n">
-        <v>23.21784816284766</v>
+        <v>5.492358917222285</v>
       </c>
       <c r="K64" t="n">
         <v>162.5786571839789</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>16.76577665973132</v>
+        <v>8.616821898348201</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F65" t="n">
-        <v>18.16510474082175</v>
+        <v>9.664928290267731</v>
       </c>
       <c r="G65" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H65" t="n">
-        <v>34.76182629088014</v>
+        <v>11.95755470981045</v>
       </c>
       <c r="I65" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="J65" t="n">
-        <v>28.84715229438877</v>
+        <v>14.38940294755902</v>
       </c>
       <c r="K65" t="n">
         <v>162.5786571839789</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>18.7637762078274</v>
+        <v>8.616821898348201</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F66" t="n">
-        <v>21.86780458407271</v>
+        <v>9.664928290267731</v>
       </c>
       <c r="G66" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H66" t="n">
-        <v>41.70897281499829</v>
+        <v>11.95755470981045</v>
       </c>
       <c r="I66" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="J66" t="n">
-        <v>32.47890917045854</v>
+        <v>14.38940294755902</v>
       </c>
       <c r="K66" t="n">
         <v>162.5786571839789</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>3.554125201770992</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>3.554125201770992</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>6.194113321114584</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>6.194113321114584</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>8.379535944734394</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>8.379535944734394</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>10.2499111483628</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>10.2499111483628</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>11.8789286489322</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>11.8789286489322</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="77">
@@ -3289,16 +3289,16 @@
         <v>162.5786571839789</v>
       </c>
       <c r="H77" t="n">
-        <v>4.874119261442788</v>
+        <v>8.908001736078264</v>
       </c>
       <c r="I77" t="n">
-        <v>3.554125201770992</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J77" t="n">
-        <v>4.874119261442788</v>
+        <v>6.715257916929008</v>
       </c>
       <c r="K77" t="n">
-        <v>3.554125201770992</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="78">
@@ -3320,22 +3320,22 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1.625115478678037</v>
       </c>
       <c r="G78" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H78" t="n">
-        <v>7.286824632924489</v>
+        <v>8.908001736078264</v>
       </c>
       <c r="I78" t="n">
-        <v>6.194113321114584</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J78" t="n">
-        <v>4.874119261442788</v>
+        <v>9.815380909477081</v>
       </c>
       <c r="K78" t="n">
-        <v>6.194113321114584</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="79">
@@ -3357,22 +3357,22 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1.625115478678037</v>
       </c>
       <c r="G79" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H79" t="n">
-        <v>7.286824632924489</v>
+        <v>8.908001736078264</v>
       </c>
       <c r="I79" t="n">
-        <v>8.379535944734394</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J79" t="n">
-        <v>4.874119261442788</v>
+        <v>9.815380909477081</v>
       </c>
       <c r="K79" t="n">
-        <v>8.379535944734394</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="80">
@@ -3394,22 +3394,22 @@
         <v>162.5786571839789</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1.625115478678037</v>
       </c>
       <c r="G80" t="n">
         <v>162.5786571839789</v>
       </c>
       <c r="H80" t="n">
-        <v>2.412705371481701</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>10.2499111483628</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>3.100122992548074</v>
       </c>
       <c r="K80" t="n">
-        <v>10.2499111483628</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>11.8789286489322</v>
+        <v>162.5786571839789</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>11.8789286489322</v>
+        <v>162.5786571839789</v>
       </c>
     </row>
     <row r="82">
@@ -3542,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5116412268396002</v>
+        <v>0.4393239936925044</v>
       </c>
       <c r="I84" t="n">
         <v>0.4822517236635052</v>
@@ -3577,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5116412268396002</v>
+        <v>0.4393239936925044</v>
       </c>
       <c r="I85" t="n">
         <v>0.5410307300156951</v>
@@ -3612,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5116412268396002</v>
+        <v>0.4393239936925044</v>
       </c>
       <c r="I86" t="n">
         <v>0.5842634421140054</v>
@@ -3717,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5116412268396002</v>
+        <v>0.4393239936925044</v>
       </c>
       <c r="I89" t="n">
         <v>0.4822517236635052</v>
@@ -3752,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5116412268396002</v>
+        <v>0.4393239936925044</v>
       </c>
       <c r="I90" t="n">
         <v>0.5410307300156951</v>
@@ -3787,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5116412268396002</v>
+        <v>0.4393239936925044</v>
       </c>
       <c r="I91" t="n">
         <v>0.5842634421140054</v>
